--- a/experiment/HAT_bestx4/Test/results-B100/B100.xlsx
+++ b/experiment/HAT_bestx4/Test/results-B100/B100.xlsx
@@ -452,10 +452,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>24.07</v>
+        <v>24.08</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5734</v>
+        <v>0.574</v>
       </c>
     </row>
     <row r="3">
@@ -465,10 +465,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>28.71</v>
+        <v>28.73</v>
       </c>
       <c r="C3" t="n">
-        <v>0.8128</v>
+        <v>0.8133</v>
       </c>
     </row>
     <row r="4">
@@ -478,10 +478,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>26.55</v>
+        <v>26.58</v>
       </c>
       <c r="C4" t="n">
-        <v>0.8139</v>
+        <v>0.8145</v>
       </c>
     </row>
     <row r="5">
@@ -494,7 +494,7 @@
         <v>30.66</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8496</v>
+        <v>0.8497</v>
       </c>
     </row>
     <row r="6">
@@ -507,7 +507,7 @@
         <v>26.26</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7118</v>
+        <v>0.7121</v>
       </c>
     </row>
     <row r="7">
@@ -520,7 +520,7 @@
         <v>33.91</v>
       </c>
       <c r="C7" t="n">
-        <v>0.8929</v>
+        <v>0.893</v>
       </c>
     </row>
     <row r="8">
@@ -530,10 +530,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>26.3</v>
+        <v>26.32</v>
       </c>
       <c r="C8" t="n">
-        <v>0.7507</v>
+        <v>0.7513</v>
       </c>
     </row>
     <row r="9">
@@ -543,10 +543,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>23.09</v>
+        <v>23.1</v>
       </c>
       <c r="C9" t="n">
-        <v>0.5911</v>
+        <v>0.5915</v>
       </c>
     </row>
     <row r="10">
@@ -556,10 +556,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>27.52</v>
+        <v>27.51</v>
       </c>
       <c r="C10" t="n">
-        <v>0.7881</v>
+        <v>0.7882</v>
       </c>
     </row>
     <row r="11">
@@ -569,10 +569,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>29.3</v>
+        <v>29.32</v>
       </c>
       <c r="C11" t="n">
-        <v>0.8027</v>
+        <v>0.8032</v>
       </c>
     </row>
     <row r="12">
@@ -582,10 +582,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>24.37</v>
+        <v>24.41</v>
       </c>
       <c r="C12" t="n">
-        <v>0.7338</v>
+        <v>0.735</v>
       </c>
     </row>
     <row r="13">
@@ -595,10 +595,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>28.06</v>
+        <v>28.07</v>
       </c>
       <c r="C13" t="n">
-        <v>0.7548</v>
+        <v>0.7561</v>
       </c>
     </row>
     <row r="14">
@@ -608,10 +608,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>30.05</v>
+        <v>30.06</v>
       </c>
       <c r="C14" t="n">
-        <v>0.8094</v>
+        <v>0.8096</v>
       </c>
     </row>
     <row r="15">
@@ -621,10 +621,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>29.58</v>
+        <v>29.6</v>
       </c>
       <c r="C15" t="n">
-        <v>0.8355</v>
+        <v>0.8364</v>
       </c>
     </row>
     <row r="16">
@@ -637,7 +637,7 @@
         <v>25.07</v>
       </c>
       <c r="C16" t="n">
-        <v>0.6798999999999999</v>
+        <v>0.6801</v>
       </c>
     </row>
     <row r="17">
@@ -647,10 +647,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>24.85</v>
+        <v>24.88</v>
       </c>
       <c r="C17" t="n">
-        <v>0.7624</v>
+        <v>0.763</v>
       </c>
     </row>
     <row r="18">
@@ -660,10 +660,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>34.82</v>
+        <v>34.85</v>
       </c>
       <c r="C18" t="n">
-        <v>0.8948</v>
+        <v>0.895</v>
       </c>
     </row>
     <row r="19">
@@ -676,7 +676,7 @@
         <v>33</v>
       </c>
       <c r="C19" t="n">
-        <v>0.8944</v>
+        <v>0.8945</v>
       </c>
     </row>
     <row r="20">
@@ -699,10 +699,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>26.04</v>
+        <v>26.05</v>
       </c>
       <c r="C21" t="n">
-        <v>0.8027</v>
+        <v>0.8028999999999999</v>
       </c>
     </row>
     <row r="22">
@@ -712,10 +712,10 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>22.19</v>
+        <v>22.21</v>
       </c>
       <c r="C22" t="n">
-        <v>0.6937</v>
+        <v>0.6953</v>
       </c>
     </row>
     <row r="23">
@@ -725,10 +725,10 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>23.98</v>
+        <v>23.97</v>
       </c>
       <c r="C23" t="n">
-        <v>0.6352</v>
+        <v>0.6347</v>
       </c>
     </row>
     <row r="24">
@@ -741,7 +741,7 @@
         <v>24.85</v>
       </c>
       <c r="C24" t="n">
-        <v>0.5734</v>
+        <v>0.5737</v>
       </c>
     </row>
     <row r="25">
@@ -751,10 +751,10 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>26.6</v>
+        <v>26.62</v>
       </c>
       <c r="C25" t="n">
-        <v>0.7922</v>
+        <v>0.7933</v>
       </c>
     </row>
     <row r="26">
@@ -767,7 +767,7 @@
         <v>27.74</v>
       </c>
       <c r="C26" t="n">
-        <v>0.8234</v>
+        <v>0.8236</v>
       </c>
     </row>
     <row r="27">
@@ -777,10 +777,10 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>27.03</v>
+        <v>27.05</v>
       </c>
       <c r="C27" t="n">
-        <v>0.8395</v>
+        <v>0.8401</v>
       </c>
     </row>
     <row r="28">
@@ -790,10 +790,10 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>27.81</v>
+        <v>27.84</v>
       </c>
       <c r="C28" t="n">
-        <v>0.7379</v>
+        <v>0.7389</v>
       </c>
     </row>
     <row r="29">
@@ -803,10 +803,10 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>29.62</v>
+        <v>29.64</v>
       </c>
       <c r="C29" t="n">
-        <v>0.8033</v>
+        <v>0.8038999999999999</v>
       </c>
     </row>
     <row r="30">
@@ -816,10 +816,10 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>32.68</v>
+        <v>32.72</v>
       </c>
       <c r="C30" t="n">
-        <v>0.9032</v>
+        <v>0.9036</v>
       </c>
     </row>
     <row r="31">
@@ -842,10 +842,10 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>29.82</v>
+        <v>29.84</v>
       </c>
       <c r="C32" t="n">
-        <v>0.8174</v>
+        <v>0.8177</v>
       </c>
     </row>
     <row r="33">
@@ -858,7 +858,7 @@
         <v>20.92</v>
       </c>
       <c r="C33" t="n">
-        <v>0.4312</v>
+        <v>0.4317</v>
       </c>
     </row>
     <row r="34">
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>25.23</v>
+        <v>25.24</v>
       </c>
       <c r="C34" t="n">
-        <v>0.6741</v>
+        <v>0.6745</v>
       </c>
     </row>
     <row r="35">
@@ -881,10 +881,10 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>24.46</v>
+        <v>24.5</v>
       </c>
       <c r="C35" t="n">
-        <v>0.7576000000000001</v>
+        <v>0.7587</v>
       </c>
     </row>
     <row r="36">
@@ -894,10 +894,10 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>35.14</v>
+        <v>35.2</v>
       </c>
       <c r="C36" t="n">
-        <v>0.8948</v>
+        <v>0.8953</v>
       </c>
     </row>
     <row r="37">
@@ -907,10 +907,10 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>26.99</v>
+        <v>27</v>
       </c>
       <c r="C37" t="n">
-        <v>0.7413999999999999</v>
+        <v>0.7419</v>
       </c>
     </row>
     <row r="38">
@@ -923,7 +923,7 @@
         <v>27.93</v>
       </c>
       <c r="C38" t="n">
-        <v>0.5135</v>
+        <v>0.5135999999999999</v>
       </c>
     </row>
     <row r="39">
@@ -933,10 +933,10 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>28.28</v>
+        <v>28.29</v>
       </c>
       <c r="C39" t="n">
-        <v>0.7186</v>
+        <v>0.7188</v>
       </c>
     </row>
     <row r="40">
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>28.52</v>
+        <v>28.53</v>
       </c>
       <c r="C40" t="n">
-        <v>0.7471</v>
+        <v>0.7474</v>
       </c>
     </row>
     <row r="41">
@@ -959,10 +959,10 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>36.06</v>
+        <v>36.12</v>
       </c>
       <c r="C41" t="n">
-        <v>0.957</v>
+        <v>0.9577</v>
       </c>
     </row>
     <row r="42">
@@ -972,10 +972,10 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>27.03</v>
+        <v>27.04</v>
       </c>
       <c r="C42" t="n">
-        <v>0.7501</v>
+        <v>0.751</v>
       </c>
     </row>
     <row r="43">
@@ -985,10 +985,10 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>25.89</v>
+        <v>25.9</v>
       </c>
       <c r="C43" t="n">
-        <v>0.7254</v>
+        <v>0.7262999999999999</v>
       </c>
     </row>
     <row r="44">
@@ -998,10 +998,10 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>26.84</v>
+        <v>26.86</v>
       </c>
       <c r="C44" t="n">
-        <v>0.763</v>
+        <v>0.7635</v>
       </c>
     </row>
     <row r="45">
@@ -1011,10 +1011,10 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>28.07</v>
+        <v>28.09</v>
       </c>
       <c r="C45" t="n">
-        <v>0.8767</v>
+        <v>0.8769</v>
       </c>
     </row>
     <row r="46">
@@ -1024,10 +1024,10 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>24.79</v>
+        <v>24.78</v>
       </c>
       <c r="C46" t="n">
-        <v>0.6842</v>
+        <v>0.6843</v>
       </c>
     </row>
     <row r="47">
@@ -1037,10 +1037,10 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>34.68</v>
+        <v>34.67</v>
       </c>
       <c r="C47" t="n">
-        <v>0.8708</v>
+        <v>0.8705000000000001</v>
       </c>
     </row>
     <row r="48">
@@ -1050,10 +1050,10 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>22.79</v>
+        <v>22.81</v>
       </c>
       <c r="C48" t="n">
-        <v>0.6268</v>
+        <v>0.6274</v>
       </c>
     </row>
     <row r="49">
@@ -1063,10 +1063,10 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>24.97</v>
+        <v>24.98</v>
       </c>
       <c r="C49" t="n">
-        <v>0.6343</v>
+        <v>0.6348</v>
       </c>
     </row>
     <row r="50">
@@ -1076,10 +1076,10 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>27.34</v>
+        <v>27.41</v>
       </c>
       <c r="C50" t="n">
-        <v>0.8773</v>
+        <v>0.8781</v>
       </c>
     </row>
     <row r="51">
@@ -1089,10 +1089,10 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>32.25</v>
+        <v>32.26</v>
       </c>
       <c r="C51" t="n">
-        <v>0.8413</v>
+        <v>0.8414</v>
       </c>
     </row>
     <row r="52">
@@ -1102,10 +1102,10 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>24.85</v>
+        <v>24.88</v>
       </c>
       <c r="C52" t="n">
-        <v>0.62</v>
+        <v>0.6215000000000001</v>
       </c>
     </row>
     <row r="53">
@@ -1115,10 +1115,10 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>22.59</v>
+        <v>22.65</v>
       </c>
       <c r="C53" t="n">
-        <v>0.706</v>
+        <v>0.7075</v>
       </c>
     </row>
     <row r="54">
@@ -1128,7 +1128,7 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>32.66</v>
+        <v>32.67</v>
       </c>
       <c r="C54" t="n">
         <v>0.8474</v>
@@ -1144,7 +1144,7 @@
         <v>32.55</v>
       </c>
       <c r="C55" t="n">
-        <v>0.8003</v>
+        <v>0.8005</v>
       </c>
     </row>
     <row r="56">
@@ -1154,10 +1154,10 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>27.75</v>
+        <v>27.76</v>
       </c>
       <c r="C56" t="n">
-        <v>0.7791</v>
+        <v>0.7798</v>
       </c>
     </row>
     <row r="57">
@@ -1167,10 +1167,10 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>25.68</v>
+        <v>25.7</v>
       </c>
       <c r="C57" t="n">
-        <v>0.6961000000000001</v>
+        <v>0.6968</v>
       </c>
     </row>
     <row r="58">
@@ -1180,10 +1180,10 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>21.46</v>
+        <v>21.47</v>
       </c>
       <c r="C58" t="n">
-        <v>0.4272</v>
+        <v>0.4283</v>
       </c>
     </row>
     <row r="59">
@@ -1193,10 +1193,10 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>27.51</v>
+        <v>27.52</v>
       </c>
       <c r="C59" t="n">
-        <v>0.7292999999999999</v>
+        <v>0.7298</v>
       </c>
     </row>
     <row r="60">
@@ -1206,10 +1206,10 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>32.03</v>
+        <v>32.04</v>
       </c>
       <c r="C60" t="n">
-        <v>0.7926</v>
+        <v>0.7927999999999999</v>
       </c>
     </row>
     <row r="61">
@@ -1219,10 +1219,10 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>31.28</v>
+        <v>31.29</v>
       </c>
       <c r="C61" t="n">
-        <v>0.7856</v>
+        <v>0.7859</v>
       </c>
     </row>
     <row r="62">
@@ -1235,7 +1235,7 @@
         <v>31.76</v>
       </c>
       <c r="C62" t="n">
-        <v>0.8155</v>
+        <v>0.8157</v>
       </c>
     </row>
     <row r="63">
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>29.01</v>
+        <v>29</v>
       </c>
       <c r="C63" t="n">
-        <v>0.7944</v>
+        <v>0.7945</v>
       </c>
     </row>
     <row r="64">
@@ -1258,10 +1258,10 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>33.84</v>
+        <v>33.86</v>
       </c>
       <c r="C64" t="n">
-        <v>0.9529</v>
+        <v>0.9530999999999999</v>
       </c>
     </row>
     <row r="65">
@@ -1271,10 +1271,10 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>24.33</v>
+        <v>24.34</v>
       </c>
       <c r="C65" t="n">
-        <v>0.6723</v>
+        <v>0.6725</v>
       </c>
     </row>
     <row r="66">
@@ -1284,10 +1284,10 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>26.05</v>
+        <v>26.06</v>
       </c>
       <c r="C66" t="n">
-        <v>0.6219</v>
+        <v>0.6222</v>
       </c>
     </row>
     <row r="67">
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>28.34</v>
+        <v>28.36</v>
       </c>
       <c r="C67" t="n">
-        <v>0.7942</v>
+        <v>0.7946</v>
       </c>
     </row>
     <row r="68">
@@ -1310,7 +1310,7 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>40</v>
+        <v>40.04</v>
       </c>
       <c r="C68" t="n">
         <v>0.9811</v>
@@ -1323,10 +1323,10 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>21.05</v>
+        <v>21.06</v>
       </c>
       <c r="C69" t="n">
-        <v>0.5819</v>
+        <v>0.5827</v>
       </c>
     </row>
     <row r="70">
@@ -1339,7 +1339,7 @@
         <v>22.79</v>
       </c>
       <c r="C70" t="n">
-        <v>0.6526999999999999</v>
+        <v>0.6529</v>
       </c>
     </row>
     <row r="71">
@@ -1349,10 +1349,10 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>28.96</v>
+        <v>28.99</v>
       </c>
       <c r="C71" t="n">
-        <v>0.8117</v>
+        <v>0.8125</v>
       </c>
     </row>
     <row r="72">
@@ -1362,10 +1362,10 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>30.57</v>
+        <v>30.59</v>
       </c>
       <c r="C72" t="n">
-        <v>0.8208</v>
+        <v>0.8216</v>
       </c>
     </row>
     <row r="73">
@@ -1378,7 +1378,7 @@
         <v>25.5</v>
       </c>
       <c r="C73" t="n">
-        <v>0.598</v>
+        <v>0.5984</v>
       </c>
     </row>
     <row r="74">
@@ -1391,7 +1391,7 @@
         <v>27.22</v>
       </c>
       <c r="C74" t="n">
-        <v>0.606</v>
+        <v>0.6063</v>
       </c>
     </row>
     <row r="75">
@@ -1401,10 +1401,10 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>26.3</v>
+        <v>26.31</v>
       </c>
       <c r="C75" t="n">
-        <v>0.6965</v>
+        <v>0.6968</v>
       </c>
     </row>
     <row r="76">
@@ -1414,10 +1414,10 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>24.17</v>
+        <v>24.18</v>
       </c>
       <c r="C76" t="n">
-        <v>0.7002</v>
+        <v>0.7012</v>
       </c>
     </row>
     <row r="77">
@@ -1427,7 +1427,7 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>30.74</v>
+        <v>30.73</v>
       </c>
       <c r="C77" t="n">
         <v>0.7859</v>
@@ -1443,7 +1443,7 @@
         <v>23.68</v>
       </c>
       <c r="C78" t="n">
-        <v>0.4801</v>
+        <v>0.4803</v>
       </c>
     </row>
     <row r="79">
@@ -1453,10 +1453,10 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>29.83</v>
+        <v>29.84</v>
       </c>
       <c r="C79" t="n">
-        <v>0.8118</v>
+        <v>0.8121</v>
       </c>
     </row>
     <row r="80">
@@ -1466,10 +1466,10 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>32.74</v>
+        <v>32.79</v>
       </c>
       <c r="C80" t="n">
-        <v>0.9528</v>
+        <v>0.9530999999999999</v>
       </c>
     </row>
     <row r="81">
@@ -1482,7 +1482,7 @@
         <v>29.77</v>
       </c>
       <c r="C81" t="n">
-        <v>0.8188</v>
+        <v>0.819</v>
       </c>
     </row>
     <row r="82">
@@ -1505,7 +1505,7 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>28.57</v>
+        <v>28.58</v>
       </c>
       <c r="C83" t="n">
         <v>0.7208</v>
@@ -1518,10 +1518,10 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>22.28</v>
+        <v>22.29</v>
       </c>
       <c r="C84" t="n">
-        <v>0.5329</v>
+        <v>0.5334</v>
       </c>
     </row>
     <row r="85">
@@ -1534,7 +1534,7 @@
         <v>21.06</v>
       </c>
       <c r="C85" t="n">
-        <v>0.6105</v>
+        <v>0.6116</v>
       </c>
     </row>
     <row r="86">
@@ -1544,10 +1544,10 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>25.74</v>
+        <v>25.72</v>
       </c>
       <c r="C86" t="n">
-        <v>0.7925</v>
+        <v>0.7923</v>
       </c>
     </row>
     <row r="87">
@@ -1557,10 +1557,10 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>25.04</v>
+        <v>25.05</v>
       </c>
       <c r="C87" t="n">
-        <v>0.6038</v>
+        <v>0.6041</v>
       </c>
     </row>
     <row r="88">
@@ -1573,7 +1573,7 @@
         <v>27.39</v>
       </c>
       <c r="C88" t="n">
-        <v>0.696</v>
+        <v>0.6962</v>
       </c>
     </row>
     <row r="89">
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>30.72</v>
+        <v>30.75</v>
       </c>
       <c r="C89" t="n">
-        <v>0.8139999999999999</v>
+        <v>0.8147</v>
       </c>
     </row>
     <row r="90">
@@ -1599,7 +1599,7 @@
         <v>27.24</v>
       </c>
       <c r="C90" t="n">
-        <v>0.5602</v>
+        <v>0.5604</v>
       </c>
     </row>
     <row r="91">
@@ -1609,10 +1609,10 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>25.12</v>
+        <v>25.14</v>
       </c>
       <c r="C91" t="n">
-        <v>0.6466</v>
+        <v>0.6478</v>
       </c>
     </row>
     <row r="92">
@@ -1625,7 +1625,7 @@
         <v>29.13</v>
       </c>
       <c r="C92" t="n">
-        <v>0.714</v>
+        <v>0.7144</v>
       </c>
     </row>
     <row r="93">
@@ -1635,10 +1635,10 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>26.73</v>
+        <v>26.72</v>
       </c>
       <c r="C93" t="n">
-        <v>0.7571</v>
+        <v>0.7574</v>
       </c>
     </row>
     <row r="94">
@@ -1648,10 +1648,10 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>30.95</v>
+        <v>30.98</v>
       </c>
       <c r="C94" t="n">
-        <v>0.8793</v>
+        <v>0.8796</v>
       </c>
     </row>
     <row r="95">
@@ -1661,7 +1661,7 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>26.01</v>
+        <v>26</v>
       </c>
       <c r="C95" t="n">
         <v>0.7171999999999999</v>
@@ -1677,7 +1677,7 @@
         <v>25.94</v>
       </c>
       <c r="C96" t="n">
-        <v>0.7988</v>
+        <v>0.8001</v>
       </c>
     </row>
     <row r="97">
@@ -1687,7 +1687,7 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>21.93</v>
+        <v>21.92</v>
       </c>
       <c r="C97" t="n">
         <v>0.3191</v>
@@ -1703,7 +1703,7 @@
         <v>27.05</v>
       </c>
       <c r="C98" t="n">
-        <v>0.5614</v>
+        <v>0.5617</v>
       </c>
     </row>
     <row r="99">
@@ -1713,10 +1713,10 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>26.33</v>
+        <v>26.34</v>
       </c>
       <c r="C99" t="n">
-        <v>0.7803</v>
+        <v>0.7808</v>
       </c>
     </row>
     <row r="100">
@@ -1729,7 +1729,7 @@
         <v>26.94</v>
       </c>
       <c r="C100" t="n">
-        <v>0.7373</v>
+        <v>0.7374000000000001</v>
       </c>
     </row>
     <row r="101">
@@ -1739,10 +1739,10 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>25</v>
+        <v>25.02</v>
       </c>
       <c r="C101" t="n">
-        <v>0.7285</v>
+        <v>0.7294</v>
       </c>
     </row>
     <row r="102">
@@ -1752,10 +1752,10 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>27.59</v>
+        <v>27.6</v>
       </c>
       <c r="C102" t="n">
-        <v>0.7375</v>
+        <v>0.7379</v>
       </c>
     </row>
   </sheetData>
